--- a/data/trans_orig/CoTrAQ-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32591</t>
+          <t>34604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>17482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36985</t>
+          <t>36479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35820</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62184</t>
+          <t>63014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27979</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51142</t>
+          <t>50986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119719</t>
+          <t>119414</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143737</t>
+          <t>142537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77741</t>
+          <t>77550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99818</t>
+          <t>99290</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>204336</t>
+          <t>204007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236611</t>
+          <t>236622</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116171</t>
+          <t>114874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161661</t>
+          <t>159018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81523</t>
+          <t>82673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118427</t>
+          <t>118686</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209052</t>
+          <t>207550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269332</t>
+          <t>266695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134521</t>
+          <t>134524</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181205</t>
+          <t>180429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96619</t>
+          <t>97107</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136382</t>
+          <t>135594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>245128</t>
+          <t>244108</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>303809</t>
+          <t>304762</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>566448</t>
+          <t>563668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>622678</t>
+          <t>622998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>310539</t>
+          <t>305627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>353569</t>
+          <t>353732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>888059</t>
+          <t>889939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>960825</t>
+          <t>963841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>37415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18903</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41958</t>
+          <t>42097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39290</t>
+          <t>39243</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71283</t>
+          <t>70624</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47245</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>38687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47365</t>
+          <t>46115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79036</t>
+          <t>79038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234894</t>
+          <t>236060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264483</t>
+          <t>265405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153826</t>
+          <t>154823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183904</t>
+          <t>183546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>400127</t>
+          <t>399601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>441062</t>
+          <t>440332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160320</t>
+          <t>159214</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>211808</t>
+          <t>211974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131116</t>
+          <t>132660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179093</t>
+          <t>181826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305366</t>
+          <t>303290</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>374520</t>
+          <t>374540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187253</t>
+          <t>185597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242835</t>
+          <t>242479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135426</t>
+          <t>133726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>180685</t>
+          <t>181042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334496</t>
+          <t>337609</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410444</t>
+          <t>410441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>943853</t>
+          <t>942484</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1012249</t>
+          <t>1011962</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>562598</t>
+          <t>560120</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>619900</t>
+          <t>619557</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1523842</t>
+          <t>1524061</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1617007</t>
+          <t>1611745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,7%</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016</t>
+          <t>CoTrAQ- Trabajo activo y posibilidades de desarrollo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38698</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62998</t>
+          <t>63034</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>20272</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36633</t>
+          <t>36408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>63253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93475</t>
+          <t>92738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39189</t>
+          <t>40328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25296</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>35291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59437</t>
+          <t>59227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>52476</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76365</t>
+          <t>76543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35639</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74886</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105966</t>
+          <t>106324</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3242,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211889</t>
+          <t>208521</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>267085</t>
+          <t>263741</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182899</t>
+          <t>183207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230037</t>
+          <t>227541</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>405915</t>
+          <t>406369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>480014</t>
+          <t>479286</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184786</t>
+          <t>187280</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>238223</t>
+          <t>237141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119671</t>
+          <t>117673</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>160473</t>
+          <t>157911</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>317726</t>
+          <t>316582</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>382716</t>
+          <t>386244</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>441578</t>
+          <t>447100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>508864</t>
+          <t>504784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>279884</t>
+          <t>286834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>333416</t>
+          <t>334618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>742162</t>
+          <t>746577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>824887</t>
+          <t>823435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>40662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70056</t>
+          <t>70069</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3713,12 +3713,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51114</t>
+          <t>51047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81202</t>
+          <t>79377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98405</t>
+          <t>99058</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139528</t>
+          <t>139604</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -3811,12 +3811,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49482</t>
+          <t>49504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81778</t>
+          <t>80229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51918</t>
+          <t>51448</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80568</t>
+          <t>79735</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107040</t>
+          <t>107848</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>149569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211807</t>
+          <t>215583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>251175</t>
+          <t>252458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161531</t>
+          <t>161428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196164</t>
+          <t>197647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>387103</t>
+          <t>385776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>438809</t>
+          <t>437800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,43%</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>309624</t>
+          <t>310199</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>377236</t>
+          <t>377949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>269005</t>
+          <t>271982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>329856</t>
+          <t>329957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>593977</t>
+          <t>594787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>685650</t>
+          <t>686103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -4267,12 +4267,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>271935</t>
+          <t>272557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335854</t>
+          <t>337242</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195169</t>
+          <t>193726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248949</t>
+          <t>246890</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>482088</t>
+          <t>486272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>565354</t>
+          <t>566719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>734295</t>
+          <t>735256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>811682</t>
+          <t>816696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>483415</t>
+          <t>482686</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>550474</t>
+          <t>546386</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1234689</t>
+          <t>1233575</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1343271</t>
+          <t>1335618</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CoTrAQ-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CoTrAQ-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36479</t>
+          <t>36036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34960</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63014</t>
+          <t>62239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>23945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28608</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50986</t>
+          <t>53310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119414</t>
+          <t>119271</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142537</t>
+          <t>143196</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77550</t>
+          <t>78023</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99290</t>
+          <t>99132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>204007</t>
+          <t>203681</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236622</t>
+          <t>235627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114874</t>
+          <t>114608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159018</t>
+          <t>159907</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82673</t>
+          <t>80754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118686</t>
+          <t>118871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207550</t>
+          <t>207841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>266695</t>
+          <t>267119</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134524</t>
+          <t>133086</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>180429</t>
+          <t>180923</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97107</t>
+          <t>96228</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>135594</t>
+          <t>134952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>244108</t>
+          <t>241941</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>304762</t>
+          <t>302922</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>563668</t>
+          <t>566515</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>622998</t>
+          <t>624341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>305627</t>
+          <t>307927</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>353732</t>
+          <t>355072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>889939</t>
+          <t>888484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>963841</t>
+          <t>964716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37415</t>
+          <t>37422</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42097</t>
+          <t>41746</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39243</t>
+          <t>39646</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70624</t>
+          <t>69559</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24515</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47494</t>
+          <t>47112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38687</t>
+          <t>41817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46115</t>
+          <t>47018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79038</t>
+          <t>78860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236060</t>
+          <t>236099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265405</t>
+          <t>265170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154823</t>
+          <t>155421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183546</t>
+          <t>183585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399601</t>
+          <t>400147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>440332</t>
+          <t>441073</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159214</t>
+          <t>157624</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>211974</t>
+          <t>210941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132660</t>
+          <t>132595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181826</t>
+          <t>180601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>303290</t>
+          <t>304313</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>374540</t>
+          <t>375149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185597</t>
+          <t>186958</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242479</t>
+          <t>244926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133726</t>
+          <t>135450</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181042</t>
+          <t>180821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337609</t>
+          <t>332896</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410441</t>
+          <t>408263</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>942484</t>
+          <t>943747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1011962</t>
+          <t>1012166</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>560120</t>
+          <t>562460</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>619557</t>
+          <t>620535</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1524061</t>
+          <t>1525582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1611745</t>
+          <t>1620072</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63034</t>
+          <t>61735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>20914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36408</t>
+          <t>37073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63253</t>
+          <t>64917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92738</t>
+          <t>92563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>20505</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40328</t>
+          <t>40114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59227</t>
+          <t>58058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52476</t>
+          <t>50928</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76543</t>
+          <t>76821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>35609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75584</t>
+          <t>77311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106324</t>
+          <t>106515</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3242,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208521</t>
+          <t>213016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263741</t>
+          <t>267739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>183207</t>
+          <t>183140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227541</t>
+          <t>230729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>406369</t>
+          <t>408201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>479286</t>
+          <t>481102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>187280</t>
+          <t>187066</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>237141</t>
+          <t>239816</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117673</t>
+          <t>115948</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>157911</t>
+          <t>159070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>316582</t>
+          <t>319587</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>386244</t>
+          <t>384262</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>447100</t>
+          <t>444208</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>504784</t>
+          <t>505310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>286834</t>
+          <t>284685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>334618</t>
+          <t>338581</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>746577</t>
+          <t>745152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>823435</t>
+          <t>824423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40662</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70069</t>
+          <t>68582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3713,12 +3713,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51047</t>
+          <t>51854</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79377</t>
+          <t>77826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99058</t>
+          <t>98913</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139604</t>
+          <t>138908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -3811,12 +3811,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>49046</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80229</t>
+          <t>78327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3826,82 +3826,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>64946</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52506</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>80702</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>17,02%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>127581</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>108006</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>150803</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>22,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>64946</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>51448</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>79735</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,06%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>127581</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>107848</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>149569</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215583</t>
+          <t>215864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>252458</t>
+          <t>252774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161428</t>
+          <t>161664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197647</t>
+          <t>195410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>385776</t>
+          <t>388638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>437800</t>
+          <t>436630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>310199</t>
+          <t>307609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>377949</t>
+          <t>375348</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>271982</t>
+          <t>271236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>329957</t>
+          <t>325983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>594787</t>
+          <t>597732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>686103</t>
+          <t>688384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -4267,12 +4267,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>272557</t>
+          <t>272484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337242</t>
+          <t>336072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193726</t>
+          <t>195453</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>246890</t>
+          <t>248218</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>486272</t>
+          <t>482546</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>566719</t>
+          <t>565581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>735256</t>
+          <t>732438</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>816696</t>
+          <t>811987</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>482686</t>
+          <t>485385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546386</t>
+          <t>548986</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1233575</t>
+          <t>1230926</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1335618</t>
+          <t>1335451</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
